--- a/src/templates/Voucher_Porting_Template_Nov.xlsx
+++ b/src/templates/Voucher_Porting_Template_Nov.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="52">
   <si>
     <t xml:space="preserve">SR_NO</t>
   </si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t xml:space="preserve">T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSN2/25-26/00699</t>
   </si>
   <si>
     <t xml:space="preserve">KO007</t>
@@ -277,16 +274,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="61.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="21.86"/>
@@ -302,7 +299,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="7.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="21.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="7.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="10.42"/>
   </cols>
   <sheetData>
@@ -685,7 +682,7 @@
         <v>34</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="U5" s="0" t="s">
         <v>29</v>
@@ -717,10 +714,10 @@
         <v>27</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>29</v>
@@ -744,7 +741,7 @@
         <v>32</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N6" s="0" t="s">
         <v>26</v>
@@ -812,7 +809,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>32</v>
@@ -845,7 +842,7 @@
         <v>34</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U7" s="0" t="s">
         <v>29</v>
@@ -892,7 +889,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>32</v>
@@ -925,7 +922,7 @@
         <v>34</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U8" s="0" t="s">
         <v>29</v>
@@ -972,7 +969,7 @@
         <v>30</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>32</v>
@@ -1005,7 +1002,7 @@
         <v>34</v>
       </c>
       <c r="T9" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U9" s="0" t="s">
         <v>29</v>
@@ -1052,7 +1049,7 @@
         <v>30</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>32</v>
@@ -1085,7 +1082,7 @@
         <v>34</v>
       </c>
       <c r="T10" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U10" s="0" t="s">
         <v>29</v>
@@ -1117,10 +1114,10 @@
         <v>27</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>29</v>
@@ -1132,7 +1129,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>32</v>
@@ -1144,7 +1141,7 @@
         <v>32</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N11" s="0" t="s">
         <v>26</v>
@@ -1165,7 +1162,7 @@
         <v>34</v>
       </c>
       <c r="T11" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U11" s="0" t="s">
         <v>29</v>
@@ -1203,7 +1200,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="29.57"/>
@@ -1215,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="D1" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="E1" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="F1" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="G1" s="0" t="s">
         <v>50</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>51</v>
       </c>
       <c r="H1" s="0" t="s">
         <v>6</v>
@@ -1247,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>29</v>
@@ -1276,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>29</v>

--- a/src/templates/Voucher_Porting_Template_Nov.xlsx
+++ b/src/templates/Voucher_Porting_Template_Nov.xlsx
@@ -113,7 +113,7 @@
     <t xml:space="preserve">NA</t>
   </si>
   <si>
-    <t xml:space="preserve">STO1008</t>
+    <t xml:space="preserve">STO1009</t>
   </si>
   <si>
     <t xml:space="preserve">AMOUNT PROVIDED FOR OFFICE PARKING RENT ADVANCE FOR THE MONTH OF November 2025 FROM OFIS SPACES PRIVATE LIMITED AGST. BILL/INVOICE NO. OSN2/25-26/01177 DATED 01-NOV-2025 STORES ENTRY / FOLIO NO. - N.A. (RENT EXPENSE) DATED - 01-NOV-2025</t>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -207,6 +207,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,8 +256,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -274,12 +283,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25"/>
@@ -485,7 +494,7 @@
       <c r="G3" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="0" t="s">
@@ -1200,7 +1209,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="29.57"/>
